--- a/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos</t>
+          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,76; 16,55</t>
+          <t>13,89; 16,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,16</t>
+          <t>10,73; 14,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 14,77</t>
+          <t>11,16; 14,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 17,18</t>
+          <t>8,38; 17,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 16,21</t>
+          <t>12,89; 16,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 12,64</t>
+          <t>9,56; 12,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 13,33</t>
+          <t>10,14; 13,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,29</t>
+          <t>8,81; 13,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,66; 15,84</t>
+          <t>13,7; 15,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 12,75</t>
+          <t>10,41; 12,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 13,27</t>
+          <t>10,95; 13,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 14,5</t>
+          <t>9,24; 14,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,74; 14,72</t>
+          <t>12,9; 14,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>11,12; 13,12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10,7; 12,19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10,51; 16,18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,38; 14,04</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,33; 13,54</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>11,07; 12,97</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10,73; 12,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10,67; 15,98</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,34; 14,03</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,29; 13,53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,09; 12,99</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 15,66</t>
+          <t>11,68; 15,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,02</t>
+          <t>12,77; 14,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 12,89</t>
+          <t>11,49; 12,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 12,3</t>
+          <t>11,08; 12,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 15,12</t>
+          <t>11,88; 14,94</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 14,33</t>
+          <t>12,59; 14,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 12,68</t>
+          <t>10,47; 12,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 11,77</t>
+          <t>10,06; 11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,05</t>
+          <t>10,19; 18,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,81; 15,36</t>
+          <t>12,83; 15,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 12,48</t>
+          <t>10,46; 12,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 12,73</t>
+          <t>10,62; 12,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,1; 19,92</t>
+          <t>10,85; 19,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 14,54</t>
+          <t>12,91; 14,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 12,09</t>
+          <t>10,71; 12,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 11,97</t>
+          <t>10,55; 11,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 17,52</t>
+          <t>11,33; 17,18</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 15,19</t>
+          <t>13,48; 15,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,52</t>
+          <t>11,49; 13,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 12,63</t>
+          <t>10,82; 12,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 24,55</t>
+          <t>12,15; 24,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 15,4</t>
+          <t>13,65; 15,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 13,64</t>
+          <t>11,99; 13,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,45</t>
+          <t>11,56; 13,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,71</t>
+          <t>9,51; 13,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 15,07</t>
+          <t>13,82; 15,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,99; 13,31</t>
+          <t>12,02; 13,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 12,69</t>
+          <t>11,35; 12,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 18,28</t>
+          <t>11,72; 18,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 14,59</t>
+          <t>13,59; 14,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,65</t>
+          <t>11,47; 12,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,07</t>
+          <t>11,08; 12,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,8</t>
+          <t>11,82; 16,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 14,51</t>
+          <t>13,41; 14,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,5</t>
+          <t>11,39; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,45</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 14,38</t>
+          <t>11,45; 14,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,37</t>
+          <t>13,63; 14,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,38</t>
+          <t>11,59; 12,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 12,11</t>
+          <t>11,34; 12,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 14,49</t>
+          <t>12,16; 14,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 16,76</t>
+          <t>13,8; 16,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 14,4</t>
+          <t>10,75; 14,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 14,53</t>
+          <t>11,24; 14,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 17,47</t>
+          <t>8,49; 17,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 16,25</t>
+          <t>12,89; 16,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 12,57</t>
+          <t>9,53; 12,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 13,3</t>
+          <t>10,14; 13,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 13,36</t>
+          <t>8,47; 13,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 15,89</t>
+          <t>13,63; 15,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,71</t>
+          <t>10,53; 12,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 13,24</t>
+          <t>10,97; 13,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,03</t>
+          <t>9,2; 13,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 14,76</t>
+          <t>12,87; 14,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 13,12</t>
+          <t>11,13; 13,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 12,19</t>
+          <t>10,66; 12,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,18</t>
+          <t>10,73; 16,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 14,04</t>
+          <t>12,39; 14,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,54</t>
+          <t>11,26; 13,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,97</t>
+          <t>11,03; 12,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 15,62</t>
+          <t>11,77; 15,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 14,03</t>
+          <t>12,79; 14,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 12,87</t>
+          <t>11,47; 12,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,35</t>
+          <t>11,09; 12,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,94</t>
+          <t>11,85; 15,02</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 14,32</t>
+          <t>12,53; 14,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,47; 12,66</t>
+          <t>10,45; 12,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 11,74</t>
+          <t>10,0; 11,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 18,3</t>
+          <t>10,24; 18,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,83; 15,35</t>
+          <t>12,91; 15,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,49</t>
+          <t>10,51; 12,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 12,65</t>
+          <t>10,68; 12,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 19,72</t>
+          <t>10,92; 19,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,91; 14,47</t>
+          <t>12,98; 14,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 12,16</t>
+          <t>10,71; 12,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 11,94</t>
+          <t>10,6; 12,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,18</t>
+          <t>11,3; 17,39</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,48; 15,28</t>
+          <t>13,44; 15,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 13,47</t>
+          <t>11,51; 13,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 12,52</t>
+          <t>10,85; 12,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 24,51</t>
+          <t>12,4; 24,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 15,42</t>
+          <t>13,7; 15,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,99; 13,68</t>
+          <t>12,01; 13,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,54</t>
+          <t>11,54; 13,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,61</t>
+          <t>9,6; 13,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 15,03</t>
+          <t>13,81; 15,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,35</t>
+          <t>12,02; 13,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 12,65</t>
+          <t>11,38; 12,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 18,69</t>
+          <t>11,66; 19,07</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,59; 14,57</t>
+          <t>13,58; 14,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,63</t>
+          <t>11,47; 12,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,05</t>
+          <t>11,07; 12,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,51</t>
+          <t>12,02; 16,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 14,53</t>
+          <t>13,46; 14,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,49</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,29; 12,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 14,27</t>
+          <t>11,61; 14,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,42</t>
+          <t>13,67; 14,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,37</t>
+          <t>11,58; 12,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,09</t>
+          <t>11,36; 12,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 14,55</t>
+          <t>12,12; 14,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
+          <t>Tiempo medio en minutos que dura el trayecto desde su domicilio a la consulta médica (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,39</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,82</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>14,97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,52</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,76</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,39</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>11,91</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,32</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,8; 16,75</t>
+          <t>12,91; 16,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 14,31</t>
+          <t>9,57; 12,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 14,64</t>
+          <t>10,1; 13,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 17,67</t>
+          <t>8,83; 13,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 16,35</t>
+          <t>13,76; 16,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 12,45</t>
+          <t>10,84; 14,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 13,23</t>
+          <t>11,18; 14,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,2</t>
+          <t>8,5; 17,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 15,76</t>
+          <t>13,66; 15,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 12,65</t>
+          <t>10,58; 12,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,12</t>
+          <t>10,96; 13,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,96</t>
+          <t>9,47; 14,98</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,27</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11,91</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13,85</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>13,63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,99</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,38</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,27</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,91</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,55</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,77</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 14,84</t>
+          <t>12,34; 14,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 13,13</t>
+          <t>11,29; 13,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,15</t>
+          <t>11,09; 12,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,18</t>
+          <t>11,92; 16,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,21</t>
+          <t>12,74; 14,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 13,49</t>
+          <t>11,07; 12,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 12,96</t>
+          <t>10,73; 12,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 15,79</t>
+          <t>10,87; 17,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 14,06</t>
+          <t>12,78; 14,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,94</t>
+          <t>11,44; 12,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 12,32</t>
+          <t>11,09; 12,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 15,02</t>
+          <t>12,04; 15,68</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,59</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14,35</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,81</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,15</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,85</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,35</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,59</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>12,83</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>13,66</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 14,33</t>
+          <t>12,81; 15,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,77</t>
+          <t>10,51; 12,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 11,84</t>
+          <t>10,6; 12,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 18,28</t>
+          <t>11,34; 20,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,91; 15,36</t>
+          <t>12,48; 14,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 12,49</t>
+          <t>10,4; 12,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,78</t>
+          <t>10,01; 11,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 19,9</t>
+          <t>9,7; 18,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 14,53</t>
+          <t>12,98; 14,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 12,12</t>
+          <t>10,64; 12,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 12,08</t>
+          <t>10,58; 11,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 17,39</t>
+          <t>11,28; 18,18</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,74</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,32</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,55</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14,27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,39</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,56</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,54</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,74</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,32</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>15,67</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,87</t>
+          <t>13,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 15,16</t>
+          <t>13,68; 15,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 13,35</t>
+          <t>11,96; 13,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 12,53</t>
+          <t>11,58; 13,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,4; 24,13</t>
+          <t>9,6; 13,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 15,48</t>
+          <t>13,44; 15,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 13,76</t>
+          <t>11,57; 13,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 13,49</t>
+          <t>10,88; 12,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 13,65</t>
+          <t>11,94; 23,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 15,03</t>
+          <t>13,84; 15,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,31</t>
+          <t>11,99; 13,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 12,64</t>
+          <t>11,35; 12,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 19,07</t>
+          <t>11,53; 17,83</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,85</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12,97</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>14,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,53</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,92</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,9</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,31</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,57</t>
+          <t>13,45; 14,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,6</t>
+          <t>11,37; 12,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,07</t>
+          <t>11,33; 12,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,59</t>
+          <t>11,65; 14,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 14,6</t>
+          <t>13,53; 14,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,47; 12,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,47</t>
+          <t>11,08; 12,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 14,21</t>
+          <t>11,96; 16,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 14,39</t>
+          <t>13,63; 14,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 12,35</t>
+          <t>11,59; 12,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 12,1</t>
+          <t>11,32; 12,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 14,64</t>
+          <t>12,14; 14,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>14,23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,39</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,97</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,52</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,91</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14,58</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11,51</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11,93</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,32</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>14.22642532275962</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.76129757482608</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>11.38903877571416</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10.82280276284161</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>14.97325154468629</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>12.31839160824898</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>12.51938207934709</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>11.90973073251139</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>14.57970482983392</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>11.5084278545216</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>11.93083684718656</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>11.32389938062093</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,91; 16,21</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 12,64</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10,1; 13,33</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8,83; 13,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,76; 16,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,84; 14,16</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 14,77</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,5; 17,78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13,66; 15,84</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10,58; 12,75</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10,96; 13,27</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,47; 14,98</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>12.91186445903464</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>9.565722306978214</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10.09890819407548</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8.833852872016658</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>13.76393380734349</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>10.84107299468522</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11.18472791838425</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.495267520026369</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>13.66053510947007</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>10.58358316984843</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>10.96142238579468</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>9.465552431594029</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16.21469024700897</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.63843225586719</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.33048875770621</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.40793668569441</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>16.54536608469116</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>14.15957398182866</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>14.76583592185303</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>17.77972821254708</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>15.84056098355722</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>12.75101007109254</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>13.26548213829547</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>14.97609828725428</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,27</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,91</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,85</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,63</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,99</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,38</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13,37</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12,13</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11,66</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>12,34; 14,03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11,29; 13,53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,09; 12,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11,92; 16,22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,74; 14,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,07; 12,97</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,73; 12,22</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 17,94</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 14,02</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11,44; 12,89</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11,09; 12,3</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,04; 15,68</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>13.12846947045924</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12.26707999498385</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>11.91065623688533</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>13.84674974984596</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>13.62645047513703</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>11.98682824359202</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>11.3803884148685</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>13.64198038314693</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>13.37106177284924</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12.1326756774091</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>11.65584336683925</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>13.76918631059558</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,59</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,41</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,23</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,81</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12,83</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>13,64</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11,29</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>12.33679978268533</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>11.28978822443996</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>11.0856670956617</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>11.91550163251774</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>12.74055401250993</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11.07439094079064</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>10.72721217187533</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>10.86645586153317</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>12.77562496111651</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>11.43722784158129</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>11.08715638737255</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>12.03555139540288</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12,81; 15,36</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10,51; 12,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10,6; 12,73</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11,34; 20,61</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>12,48; 14,33</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>10,4; 12,68</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,01; 11,77</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 18,39</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12,98; 14,54</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>10,64; 12,09</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>10,58; 11,97</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>11,28; 18,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.02823422433856</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>13.5270821165138</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>12.99481155414142</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.2171828657767</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>14.724316714847</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>12.96807383483134</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>12.21954591730759</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>17.94039483866612</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>14.02286448534423</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>12.88526912822189</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>12.30070640933789</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>15.68446742631543</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14,54</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,74</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,32</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,27</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,39</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,56</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,67</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14,4</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12,57</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11,93</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,74</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>13.84520886201221</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>11.34889176996092</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>11.59011911653067</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>14.346025423314</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>13.41113606164893</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>11.23445464814563</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>10.81032789222621</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>12.82807634315905</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>13.63507138429478</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>11.29441128498855</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>11.21265059461951</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>13.65786625420252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13,68; 15,4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11,96; 13,64</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,58; 13,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,6; 13,77</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,44; 15,19</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,57; 13,52</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,88; 12,63</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11,94; 23,57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13,84; 15,07</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11,99; 13,31</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11,35; 12,69</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,53; 17,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>12.81496676913037</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>10.50917435546211</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>10.59589786949416</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>11.33582882053839</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>12.48331123656767</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>10.3969353518183</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10.00851726333612</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.695548879745802</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>12.97855572607834</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>10.63901937473504</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>10.5798897628705</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>11.28251343089647</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.35740444277895</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.47978976855904</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.7298408332423</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.60603801270537</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>14.33284157477586</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>12.67772016275976</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>11.76619986730182</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>18.39384247539082</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>14.54126650655609</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>12.08753463598629</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>11.97283601537442</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>18.18079584531799</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>14.53610338770158</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>12.74248063040973</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>12.32036406152451</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>11.54514655496064</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>14.27410004831036</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>12.39313248588546</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>11.55551117111136</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>15.66565796323983</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>14.40229436609127</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>12.56777342879213</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>11.93340772908401</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>13.73659442616861</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>13.68251116193597</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>11.95732650553435</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>11.57807791238439</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>9.604102769634631</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>13.4448589445775</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.57020754381346</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>10.8773301403547</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>11.94225412841129</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>13.83554448293539</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>11.98515506287463</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>11.35119616723772</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>11.5328056918356</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.40196074120332</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>13.6375430590771</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>13.44569259840982</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>13.76625533573467</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>15.19295707559241</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>13.5174171602477</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>12.63353245140928</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>23.56732402821162</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>15.07318006917075</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>13.30756364780825</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>12.69340630520718</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>17.82619427421067</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,92</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,04</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,53</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13,98</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11,69</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>13,45; 14,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11,37; 12,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 12,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11,65; 14,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,53; 14,59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,47; 12,65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,08; 12,07</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11,96; 16,86</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13,63; 14,37</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11,59; 12,38</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11,32; 12,11</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,14; 14,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>13.92103071657277</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>11.90391717788057</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>11.85040433136647</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>12.96750362173543</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>14.04437981032134</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>12.02288604179287</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>11.52944666064165</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>13.71931023165148</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>13.98157981034621</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>11.96161509590315</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>11.693703793222</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>13.30503018326292</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>13.44890842173381</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>11.37385004840927</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>11.33343395249603</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>11.6506891724136</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>13.53059226186534</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>11.46951661894438</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>11.08401096954695</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>11.95575165745194</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>13.62618824079139</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>11.58538125561825</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>11.32382013119831</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>12.13938202892009</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.50898756321102</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.49966560736521</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>12.44983585425031</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>14.70568462762993</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>14.58879493748012</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>12.65209444523252</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>12.0732040857605</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>16.85542541423531</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>14.37008663748824</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>12.37816765986172</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>12.11308658897577</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>14.82787926282703</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
